--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
         <v>19.39393939393938</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>29.37062937062937</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         <v>23.78378378378379</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         <v>14.36781609195403</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>27.71084337349399</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +552,7 @@
         <v>20.38369304556353</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -579,7 +579,7 @@
         <v>10.33868092691623</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -606,7 +606,7 @@
         <v>24.66124661246612</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -633,13 +633,13 @@
         <v>17.22595078299778</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="C11">
-        <v>5.92</v>
+        <v>6.05</v>
       </c>
       <c r="D11">
-        <v>5.28</v>
+        <v>5.33</v>
       </c>
       <c r="E11">
-        <v>0.6399999999999997</v>
+        <v>0.7199999999999998</v>
       </c>
       <c r="F11">
-        <v>12.12121212121211</v>
+        <v>13.50844277673546</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -675,25 +675,25 @@
         </is>
       </c>
       <c r="C12">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="D12">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="E12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="F12">
-        <v>31.50684931506849</v>
+        <v>27.74725274725276</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,22 +705,22 @@
         <v>5.26</v>
       </c>
       <c r="D13">
-        <v>4.32</v>
+        <v>4.37</v>
       </c>
       <c r="E13">
-        <v>0.9399999999999995</v>
+        <v>0.8899999999999997</v>
       </c>
       <c r="F13">
-        <v>21.75925925925926</v>
+        <v>20.36613272311212</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marga Marga</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -729,25 +729,25 @@
         </is>
       </c>
       <c r="C14">
-        <v>5.74</v>
+        <v>5.92</v>
       </c>
       <c r="D14">
-        <v>5.26</v>
+        <v>5.28</v>
       </c>
       <c r="E14">
-        <v>0.4800000000000004</v>
+        <v>0.6399999999999997</v>
       </c>
       <c r="F14">
-        <v>9.125475285171113</v>
+        <v>12.12121212121211</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marga Marga</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -756,25 +756,25 @@
         </is>
       </c>
       <c r="C15">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="D15">
-        <v>3.86</v>
+        <v>3.65</v>
       </c>
       <c r="E15">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="F15">
-        <v>26.42487046632125</v>
+        <v>31.50684931506849</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marga Marga</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -786,22 +786,22 @@
         <v>5.26</v>
       </c>
       <c r="D16">
-        <v>4.48</v>
+        <v>4.32</v>
       </c>
       <c r="E16">
-        <v>0.7799999999999994</v>
+        <v>0.9399999999999995</v>
       </c>
       <c r="F16">
-        <v>17.41071428571428</v>
+        <v>21.75925925925926</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Marga Marga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -810,25 +810,25 @@
         </is>
       </c>
       <c r="C17">
-        <v>6.7</v>
+        <v>5.74</v>
       </c>
       <c r="D17">
-        <v>5.76</v>
+        <v>5.26</v>
       </c>
       <c r="E17">
-        <v>0.9400000000000004</v>
+        <v>0.4800000000000004</v>
       </c>
       <c r="F17">
-        <v>16.31944444444444</v>
+        <v>9.125475285171113</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Marga Marga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -837,25 +837,25 @@
         </is>
       </c>
       <c r="C18">
-        <v>5.89</v>
+        <v>4.88</v>
       </c>
       <c r="D18">
-        <v>4.59</v>
+        <v>3.86</v>
       </c>
       <c r="E18">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="F18">
-        <v>28.32244008714597</v>
+        <v>26.42487046632125</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Marga Marga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="C19">
-        <v>6.24</v>
+        <v>5.26</v>
       </c>
       <c r="D19">
-        <v>5.09</v>
+        <v>4.48</v>
       </c>
       <c r="E19">
-        <v>1.15</v>
+        <v>0.7799999999999994</v>
       </c>
       <c r="F19">
-        <v>22.5933202357564</v>
+        <v>17.41071428571428</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="C20">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="D20">
-        <v>5.99</v>
+        <v>5.76</v>
       </c>
       <c r="E20">
-        <v>0.9100000000000001</v>
+        <v>0.9400000000000004</v>
       </c>
       <c r="F20">
-        <v>15.19198664440735</v>
+        <v>16.31944444444444</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -921,22 +921,22 @@
         <v>5.89</v>
       </c>
       <c r="D21">
-        <v>4.51</v>
+        <v>4.59</v>
       </c>
       <c r="E21">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="F21">
-        <v>30.59866962305986</v>
+        <v>28.32244008714597</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -945,25 +945,25 @@
         </is>
       </c>
       <c r="C22">
-        <v>6.3</v>
+        <v>6.24</v>
       </c>
       <c r="D22">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="E22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="F22">
-        <v>22.80701754385965</v>
+        <v>22.5933202357564</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="C23">
-        <v>6.88</v>
+        <v>6.9</v>
       </c>
       <c r="D23">
-        <v>4.78</v>
+        <v>5.99</v>
       </c>
       <c r="E23">
-        <v>2.1</v>
+        <v>0.9100000000000001</v>
       </c>
       <c r="F23">
-        <v>43.93305439330544</v>
+        <v>15.19198664440735</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -999,45 +999,126 @@
         </is>
       </c>
       <c r="C24">
-        <v>7.31</v>
+        <v>5.89</v>
       </c>
       <c r="D24">
-        <v>5.34</v>
+        <v>4.51</v>
       </c>
       <c r="E24">
-        <v>1.97</v>
+        <v>1.38</v>
       </c>
       <c r="F24">
-        <v>36.89138576779025</v>
+        <v>30.59866962305986</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Petorca</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>6.3</v>
+      </c>
+      <c r="D25">
+        <v>5.13</v>
+      </c>
+      <c r="E25">
+        <v>1.17</v>
+      </c>
+      <c r="F25">
+        <v>22.80701754385965</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Isla de Pascua</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>6.88</v>
+      </c>
+      <c r="D26">
+        <v>4.78</v>
+      </c>
+      <c r="E26">
+        <v>2.1</v>
+      </c>
+      <c r="F26">
+        <v>43.93305439330544</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Isla de Pascua</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>7.31</v>
+      </c>
+      <c r="D27">
+        <v>5.34</v>
+      </c>
+      <c r="E27">
+        <v>1.97</v>
+      </c>
+      <c r="F27">
+        <v>36.89138576779025</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Isla de Pascua</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C25">
+      <c r="C28">
         <v>7.09</v>
       </c>
-      <c r="D25">
+      <c r="D28">
         <v>5.06</v>
       </c>
-      <c r="E25">
+      <c r="E28">
         <v>2.03</v>
       </c>
-      <c r="F25">
+      <c r="F28">
         <v>40.11857707509883</v>
       </c>
-      <c r="G25">
+      <c r="G28">
         <v>1</v>
       </c>
     </row>
@@ -1140,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1597,6 +1678,60 @@
         <v>1</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>5.89</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>4.37</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>5.26</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:22</t>
+    <t xml:space="preserve">2026-08-19 15:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -98,13 +98,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_peringrmin_a_2024_valparaiso.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -1193,23 +1199,23 @@
         <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1232,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -1313,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
@@ -1324,7 +1330,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>7.48</v>
@@ -1335,7 +1341,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>5.06</v>
@@ -1346,7 +1352,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>7.09</v>
@@ -1357,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>5.16</v>
@@ -1368,7 +1374,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>3.7</v>
@@ -1379,7 +1385,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>4.58</v>
@@ -1390,7 +1396,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>6</v>
@@ -1401,7 +1407,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>4.48</v>
@@ -1412,7 +1418,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>5.26</v>
@@ -1423,7 +1429,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>7.13</v>
@@ -1434,7 +1440,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>5.13</v>
@@ -1445,7 +1451,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>6.3</v>
@@ -1456,7 +1462,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>6</v>
@@ -1467,7 +1473,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>4.47</v>
@@ -1478,7 +1484,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>5.24</v>
@@ -1489,7 +1495,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>7.19</v>
@@ -1500,7 +1506,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>5.09</v>
@@ -1511,7 +1517,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>6.24</v>
@@ -1522,7 +1528,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>6.2</v>
@@ -1533,7 +1539,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>4.32</v>
@@ -1544,7 +1550,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>5.26</v>
@@ -1555,7 +1561,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>5.45</v>
@@ -1566,7 +1572,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>4.17</v>
@@ -1577,7 +1583,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>5.02</v>
@@ -1588,7 +1594,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>5.89</v>
@@ -1599,7 +1605,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C27" s="2" t="n">
         <v>4.37</v>
@@ -1610,7 +1616,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>5.26</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 15:22</t>
+    <t xml:space="preserve">2026-09-07 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
